--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487006_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487006_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1561</v>
+        <v>7.7666</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1495</v>
+        <v>5.9675</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0066</v>
+        <v>1.7991</v>
       </c>
       <c r="G2" t="n">
         <v>5.0826</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0201</v>
+        <v>0.6306</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6856</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3346</v>
+        <v>0.1271</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8315</v>
+        <v>5.7334</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5279</v>
+        <v>4.4892</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3035</v>
+        <v>1.2442</v>
       </c>
       <c r="G3" t="n">
         <v>4.9303</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.179</v>
+        <v>-0.277</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4147</v>
+        <v>-0.4535</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2358</v>
+        <v>0.1765</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7763</v>
+        <v>2.2244</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6942</v>
+        <v>3.1126</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9179</v>
+        <v>-0.8883</v>
       </c>
       <c r="G4" t="n">
         <v>1.5512</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.1482</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5192</v>
+        <v>-0.1008</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.077</v>
+        <v>-0.0474</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2819</v>
+        <v>1.5133</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.246</v>
+        <v>0.1336</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5279</v>
+        <v>1.3797</v>
       </c>
       <c r="G5" t="n">
         <v>2.6941</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0015</v>
+        <v>-0.77</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.178</v>
+        <v>-0.7983</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1765</v>
+        <v>0.0283</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1012</v>
+        <v>0.0624</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7081</v>
+        <v>-0.7468</v>
       </c>
       <c r="F6" t="n">
         <v>0.8093</v>
@@ -922,10 +922,10 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6819</v>
+        <v>0.6432</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6469</v>
+        <v>0.6082</v>
       </c>
       <c r="U6" t="n">
         <v>0.035</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4078</v>
+        <v>-1.5017</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8025</v>
+        <v>-0.1755</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6053</v>
+        <v>-1.3262</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.9847</v>
+        <v>0.6189</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2061</v>
+        <v>-0.052</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7786</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6043</v>
+        <v>0.7731</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9859</v>
+        <v>0.221</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.5522</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3804</v>
+        <v>-0.1542</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2201</v>
+        <v>-0.2729</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1602</v>
+        <v>0.1188</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.5046</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.1315</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0464</v>
+        <v>-0.6362</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4845</v>
+        <v>-2.6748</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5651</v>
+        <v>-2.0222</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9194</v>
+        <v>-0.6526</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2817</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0847</v>
+        <v>-0.1056</v>
       </c>
       <c r="T8" t="n">
-        <v>0.98</v>
+        <v>0.5228</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8952</v>
+        <v>-0.6284</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6982</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8804</v>
+        <v>-3.3319</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2874</v>
+        <v>-1.4301</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.593</v>
+        <v>-1.9018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6189</v>
+        <v>-3.9847</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.052</v>
+        <v>-2.2061</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6709000000000001</v>
+        <v>-1.7786</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7731</v>
+        <v>-1.6043</v>
       </c>
       <c r="K9" t="n">
-        <v>0.221</v>
+        <v>-0.9859</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5522</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1542</v>
+        <v>-2.3804</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2729</v>
+        <v>-1.2201</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1188</v>
+        <v>-1.1602</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8833</v>
+        <v>-0.1685</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9804</v>
+        <v>0.1742</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9029</v>
+        <v>-0.3428</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7285</v>
+        <v>-3.3579</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4298</v>
+        <v>-3.0888</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2987</v>
+        <v>-0.269</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4933</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9334</v>
+        <v>-0.5628</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.651</v>
+        <v>-0.31</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2824</v>
+        <v>-0.2527</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0698</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7789</v>
+        <v>-3.9083</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2765</v>
+        <v>-3.5245</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5024</v>
+        <v>-0.3838</v>
       </c>
       <c r="G11" t="n">
         <v>-1.959</v>
@@ -1312,13 +1312,13 @@
         <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-1.1197</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1862</v>
+        <v>-0.4342</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8041</v>
+        <v>-0.6856</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8295</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.866899999999999</v>
+        <v>2.525499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.056199999999999</v>
+        <v>2.715000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1893999999999996</v>
+        <v>-0.1894</v>
       </c>
       <c r="G12" t="n">
         <v>4.709000000000001</v>
@@ -1390,19 +1390,19 @@
         <v>14.3741</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.041700000000001</v>
+        <v>-2.3826</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8151000000000003</v>
+        <v>-0.1566</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2261</v>
+        <v>-2.2262</v>
       </c>
       <c r="V12" t="n">
         <v>-3.9075</v>
       </c>
       <c r="W12" t="n">
-        <v>4.845899999999999</v>
+        <v>4.8459</v>
       </c>
       <c r="X12" t="n">
         <v>-8.753400000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5868</v>
+        <v>5.0721</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3668</v>
+        <v>3.6362</v>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>1.4359</v>
       </c>
       <c r="G13" t="n">
-        <v>2.433</v>
+        <v>2.4148</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6644</v>
+        <v>1.3726</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7685999999999999</v>
+        <v>1.0422</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4454</v>
+        <v>1.8456</v>
       </c>
       <c r="K13" t="n">
-        <v>0.656</v>
+        <v>0.5037</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7893</v>
+        <v>1.3418</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9877</v>
+        <v>0.5693</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0084</v>
+        <v>0.8689</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0207</v>
+        <v>-0.2996</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>3.817</v>
+        <v>1.4868</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8435</v>
+        <v>0.8173</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9735</v>
+        <v>0.6695</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1314</v>
+        <v>0.3491</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.1786</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1786</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7844</v>
+        <v>4.9201</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6362</v>
+        <v>2.7978</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1482</v>
+        <v>2.1223</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4148</v>
+        <v>2.433</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3726</v>
+        <v>1.6644</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0422</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8456</v>
+        <v>1.4454</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5037</v>
+        <v>0.656</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3418</v>
+        <v>0.7893</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5693</v>
+        <v>0.9877</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8689</v>
+        <v>1.0084</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2996</v>
+        <v>-0.0207</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1991</v>
+        <v>2.1503</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8173</v>
+        <v>1.2745</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3818</v>
+        <v>0.8758</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3491</v>
+        <v>0.1314</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8295</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0239</v>
+        <v>2.3315</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8902</v>
+        <v>1.6224</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1337</v>
+        <v>0.7091</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5008</v>
@@ -1624,13 +1624,13 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9762999999999999</v>
+        <v>0.3313</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8486</v>
+        <v>-0.1164</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1277</v>
+        <v>0.4477</v>
       </c>
       <c r="V15" t="n">
         <v>2.7063</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1315</v>
+        <v>-0.0776</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4858</v>
+        <v>-0.0674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3543</v>
+        <v>-0.0102</v>
       </c>
       <c r="G16" t="n">
         <v>0.5614</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8266</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3489</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1754</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6982</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3611</v>
+        <v>-0.3255</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0451</v>
+        <v>0.7917</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3159</v>
+        <v>-1.1172</v>
       </c>
       <c r="G17" t="n">
         <v>0.9829</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2003</v>
+        <v>-0.1647</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7827</v>
+        <v>0.0541</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4175</v>
+        <v>-0.2188</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9384</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6706</v>
+        <v>-1.5764</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0798</v>
+        <v>-1.1844</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5907</v>
+        <v>-0.392</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0626</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.224</v>
+        <v>-0.1298</v>
       </c>
       <c r="T18" t="n">
-        <v>0.244</v>
+        <v>0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4679</v>
+        <v>-0.2692</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9352</v>
+        <v>-1.9062</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3646</v>
+        <v>-1.0608</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4294</v>
+        <v>-0.8454</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0778</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8437</v>
+        <v>-0.6197</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2341</v>
+        <v>-0.3314</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7731</v>
+        <v>0.0589</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.963</v>
+        <v>0.0195</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7361</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8509</v>
+        <v>-1.0101</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1194</v>
+        <v>-0.6392</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9702</v>
+        <v>-0.3709</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.6962</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.5442</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4199</v>
+        <v>-0.1337</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9877</v>
+        <v>-0.093</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4322</v>
+        <v>-0.0407</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0701</v>
+        <v>-2.0659</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1654</v>
+        <v>-2.783</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9046999999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-1.0778</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6197</v>
+        <v>-0.8437</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3314</v>
+        <v>-0.2341</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0589</v>
+        <v>0.7731</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0195</v>
+        <v>-0.963</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>1.7361</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0101</v>
+        <v>-1.8509</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6392</v>
+        <v>0.1194</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3709</v>
+        <v>-1.9702</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8214</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-5.5442</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2976</v>
+        <v>1.2892</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1976</v>
+        <v>0.5693</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0999</v>
+        <v>0.7199</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7607</v>
+        <v>-3.1129</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5592</v>
+        <v>-0.873</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2015</v>
+        <v>-2.2399</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0571</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0527</v>
+        <v>-0.4049</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1045</v>
+        <v>-0.2093</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1572</v>
+        <v>-0.1956</v>
       </c>
       <c r="V21" t="n">
         <v>0.9384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3329</v>
+        <v>-3.7314</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0039</v>
+        <v>-2.6901</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3291</v>
+        <v>-1.0414</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4519</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4703</v>
+        <v>-0.8688</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.5898</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.867</v>
+        <v>-0.4722</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1894000000000013</v>
+        <v>0.1894000000000009</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.056299999999999</v>
+        <v>-0.6617</v>
       </c>
       <c r="G23" t="n">
         <v>-4.709200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>10.267</v>
       </c>
       <c r="S23" t="n">
-        <v>3.0414</v>
+        <v>4.4362</v>
       </c>
       <c r="T23" t="n">
         <v>2.2264</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8152000000000001</v>
+        <v>2.209800000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.907500000000001</v>
